--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。rtf_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。rtf_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。table_plan(data; spec = read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>tfl_plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>tfl_plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col の値ごとに改ページ（tfl_plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>plan_blanks() の where / first / last / counted。</t>
+          <t>tfl_plan_blanks() の where / first / last / counted。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>tfl_plan_stub() の vars / into / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
+          <t>tfl_plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>以下は表の周りの定義。read_report_spec(c(report.xlsx; tables.xlsx); output_id = ) で 1 冊でも分冊でも読める。同じシートに行があるのは 1 冊だけにする（空のシートと study は重なってよい）。rtf_report(spec; plan) で rtf_document、report_path(spec) で出力先。</t>
+          <t>以下は表の周りの定義。tfl_read_report_spec(c(report.xlsx; tables.xlsx); output_id = ) で 1 冊でも分冊でも読める。同じシートに行があるのは 1 冊だけにする（空のシートと study は重なってよい）。tfl_report(spec; plan) で rtf_document、tfl_report_path(spec) で出力先。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
+          <t>rtfreporter の表の定義ファイル（table spec）（spec_version 1）。tfl_table_plan(data; tfl_read_table_spec(path; output_id = )) で読む。名前が _ で始まるシートは読まれない（このシート）。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_plan(data; spec = tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
+          <t>ここまでの 4 シートで table data.frame、以下の 4 シート（layout / columns / style / col_header）で列ヘッダー付きの rtftable のページまで。tfl_table_plan(data; tfl_read_table_spec(path; output_id = )) で読む。後に書いた plan_*() が勝つ。</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tfl_plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tfl_plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（tfl_plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tfl_plan_blanks() の where / first / last / counted。</t>
+          <t>plan_blanks() の where / first / last / counted。</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tfl_plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tfl_plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
+          <t>plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cells（テンプレートでセルを作る）/ rows（統計量ごとに 1 行、生の値）。</t>
+          <t>cells（テンプレートでセルを作る）/ rows（統計量ごとに 1 行、生の値）。plan_cells(stats = )。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>stats = rows のときの値。stat（数値）/ stat_fmt（cards 整形済み文字列）。</t>
+          <t>stats = rows のときの値。stat（数値）/ stat_fmt（cards 整形済み文字列）。plan_cells(value = )。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cols が複数のとき列名をつなぐ文字。既定は ____。</t>
+          <t>cols が複数のとき値の列名をつなぐ文字。既定は ____。columns シートはこの名前で列を指す。plan_columns(sep = )。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>列方向に合計して .sort_stat 列にする統計量名。</t>
+          <t>列方向に合計して並べ替えに使う統計量名。plan_sort(stat = )。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ページ（検査項目など）で分けた表のヘッダー {n} がどの母集団か。page = そのページの母集団（その検査を受けた人）/ table = 解析対象集団（ページキーを持たない ARD 行）。両方なら n = page | N = table で {n} と {N}。空欄 = page（両方あって食い違えば警告）。どちらも ARD に入れておくこと。</t>
+          <t>ページ（検査項目など）で分けた表のヘッダー {n} がどの母集団か。page = そのページの母集団（その検査を受けた人）/ table = 解析対象集団（ページキーを持たない ARD 行）。両方なら n = page | N = table で {n} と {N}。空欄 = page（両方あって食い違えば警告）。どちらも ARD に入れておくこと。plan_col_header(values = list(n = ...))。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>stats = rows の帳票だけ：統計量ごとの表示桁。row = 統計量名（ラベル列の値）、digits / signif を書く（fmt_numeric と同じ）。variable / context は空欄。</t>
+          <t>stats = rows の帳票だけ：統計量ごとの表示桁。row = 統計量名（ラベル列の値）、digits / signif を書く（plan_digits(.rows = ) になる。signif は 4s のように有効桁）。variable / context は空欄。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pages_max_rows / pages_split / pages_by / pages_min_group_rows / pages_cont_label</t>
+          <t>pages_max_rows / pages_split / pages_min_group_rows / pages_cont_label</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>plan_paginate_rows() の max_rows / split / by / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。</t>
+          <t>plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>group_col / group_mode / group_collapse</t>
+          <t>group_mode / group_collapse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>plan_row_group() の col / mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。</t>
+          <t>plan_row_group() の mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。グループの列は行キーから決まる。</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>group_page / group_show</t>
+          <t>group_page / group_col / group_keep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>group_page = TRUE で group_col の値ごとに改ページ（plan_paginate_group）。group_show = FALSE でその列を表示しない。</t>
+          <t>group_page = TRUE で group_col（空欄なら一番外の行キー）の値ごとに改ページ（plan_paginate_group の col / keep）。group_keep = FALSE でその列を表示しない。</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRUE / FALSE</t>
+          <t>TRUE / PARAM / FALSE</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>stub_vars / stub_into / stub_indent / stub_summary / stub_before</t>
+          <t>stub_vars / stub_name / stub_indent / stub_summary / stub_before</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>plan_stub() の vars / into / indent / group_summary / before。</t>
+          <t>plan_stub() の vars / name / indent / group_summary / before。</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 行 = 印字される列 1 つ。列は名前で指定（畳んだスタブは stub_into の名前）。.values = 展開された値の列すべて。</t>
+          <t>1 行 = 印字される列 1 つ。列は名前で指定（畳んだスタブは stub_name の名前、値の列は tables の sep でつないだ名前）。.values = 展開された値の列すべて。</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TRUE で行見出しの列。</t>
+          <t>TRUE で行見出しの列。plan_columns(row_title = )。</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 行 = 1 帳票。border / align_count_pct / auto_width / row_height_twips / header_row_height_twips / blank_row_height_twips / font / font_size_half_points / table_align / cell_valign（rtftable と同じ引数）。</t>
+          <t>1 行 = 1 帳票。border / align_count_pct / row_height_twips / header_row_height_twips / blank_row_height_twips / font / font_size_half_points / table_align / cell_valign（plan_style と同じ引数）。auto_width は plan_columns(auto_width = ) になる。</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2255,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2276,105 +2276,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pages_by</t>
+          <t>pages_min_group_rows</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pages_min_group_rows</t>
+          <t>pages_cont_label</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>pages_cont_label</t>
+          <t>group_col</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>group_col</t>
+          <t>group_mode</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>group_mode</t>
+          <t>group_collapse</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>group_collapse</t>
+          <t>group_page</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>group_page</t>
+          <t>group_keep</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>group_show</t>
+          <t>blank_where</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>blank_where</t>
+          <t>blank_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>blank_first</t>
+          <t>blank_last</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>blank_last</t>
+          <t>blank_counted</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>blank_counted</t>
+          <t>stub_vars</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>stub_vars</t>
+          <t>stub_name</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>stub_into</t>
+          <t>stub_indent</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>stub_indent</t>
+          <t>stub_summary</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>stub_summary</t>
+          <t>stub_before</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>stub_before</t>
+          <t>colpages_every</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>colpages_every</t>
+          <t>colpages_at</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>colpages_at</t>
+          <t>colpages_keep</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>colpages_carry</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>colpages_order</t>
         </is>
@@ -2386,27 +2381,27 @@
           <t>LB</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>row_label</t>
         </is>
@@ -2495,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2526,32 +2521,82 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>row_height_exact</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>header_row_height_twips</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>blank_row_height_twips</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cell_padding_left_twips</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cell_padding_right_twips</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>font</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>font_size_half_points</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>table_align</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cell_valign</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>markup</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>blank_row_normalize</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>border_header</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>border_spanning</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>border_body</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>border_first_row</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>border_last_row</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/ard-spec/LB.xlsx
+++ b/inst/extdata/ard-spec/LB.xlsx
@@ -13,8 +13,9 @@
     <sheet name="layout" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="columns" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="style" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="col_header" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="about" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="cell_styles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="col_header" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="about" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -33,7 +34,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">id: the subject key (USUBJID); output: where the study ARD goes</t>
+          <t xml:space="preserve">The fact: rounding (r: round half to even; sas: round half away from zero; blank: options(rtfreporter.rounding)); output_path (the folder of the RTF files); program_dir (the folder of the programs, for {PROGRAM}); ARD: id (the subject key; default USUBJID), output (the study ARD's file; default output/ard/ard.rds), source (R files of the study's own analysis functions, relative to the study folder, | between them).
+Example: rounding</t>
         </r>
       </text>
     </comment>
@@ -45,7 +47,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">id: the subject key (USUBJID); output: where the study ARD goes</t>
+          <t xml:space="preserve">Its value, as text.
+Example: sas</t>
         </r>
       </text>
     </comment>
@@ -59,6 +62,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -67,8 +83,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">横に展開するキー。外側から順に。
-例: TR01AG1 | SEROSTAT</t>
+          <t xml:space="preserve">The key spread across the columns, outermost first, | between them (table_plan(cols = )).
+Example: TRT01A | SEROSTAT</t>
         </r>
       </text>
     </comment>
@@ -80,8 +96,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">縦のキー。name = 列名 で列名を付け替え。引用符で囲んだ値は固定の見出し。
-例: group1 = AEBODSYS | grp = "Worst Post-Baseline Values"</t>
+          <t xml:space="preserve">The keys down the rows (table_plan(rows = )); name = column renames, a quoted value is a constant heading; | between them.
+Example: group1 = AEBODSYS | grp = "Worst Post-Baseline Values"</t>
         </r>
       </text>
     </comment>
@@ -93,8 +109,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">行ラベルの元。空欄 = .label。NA = 行の区別にだけ使って列は出さない。NULL = 使わない。
-例: label = AEDECOD</t>
+          <t xml:space="preserve">Where the row label comes from (table_plan(label = )); blank: .label; NA: used to tell rows apart, not printed; NULL: not used.
+Example: label = AEDECOD</t>
         </r>
       </text>
     </comment>
@@ -106,8 +122,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">cells（テンプレートでセルを作る）/ rows（統計量ごとに 1 行、生の値）。plan_cells(stats = )。
-例: rows</t>
+          <t xml:space="preserve">cells (cells built from templates) or rows (one statistic a row, the raw values) (plan_cells(stats = )); blank: cells.
+Example: rows</t>
         </r>
       </text>
     </comment>
@@ -119,8 +135,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">stats = rows のときの値。stat（数値）/ stat_fmt（cards 整形済み文字列）。plan_cells(value = )。
-例: stat</t>
+          <t xml:space="preserve">With stats = rows: stat (the number) or stat_fmt (cards' formatted text) (plan_cells(value = )); blank: stat.
+Example: stat</t>
         </r>
       </text>
     </comment>
@@ -132,8 +148,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">cols が複数のとき値の列名をつなぐ文字。既定は ____。columns シートはこの名前で列を指す。plan_columns(sep = )。
-例: _</t>
+          <t xml:space="preserve">What joins several column keys into a column name (plan_columns(sep = )); the columns sheet names value columns with it; blank: ____.
+Example: _</t>
         </r>
       </text>
     </comment>
@@ -145,8 +161,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">TRUE / FALSE / 並べ替えキーの列挙。
-例: .overall | group1 | .depth | -n | label</t>
+          <t xml:space="preserve">TRUE, FALSE, or the sort keys in order, - in front for descending (plan_sort()); blank: the data's order.
+Example: .overall | group1 | -n | label</t>
         </r>
       </text>
     </comment>
@@ -158,8 +174,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">列方向に合計して並べ替えに使う統計量名。plan_sort(stat = )。
-例: n</t>
+          <t xml:space="preserve">The statistic totalled across columns for a frequency order (plan_sort(stat = )).
+Example: n</t>
         </r>
       </text>
     </comment>
@@ -171,8 +187,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">どのテンプレートも埋められなかったセルの値。
-例: -</t>
+          <t xml:space="preserve">What a cell no template could fill prints (plan_cells(na = )); blank: empty.
+Example: -</t>
         </r>
       </text>
     </comment>
@@ -184,8 +200,20 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">ページ（検査項目など）で分けた表のヘッダー {n} がどの母集団か。page = そのページの母集団（その検査を受けた人）/ table = 解析対象集団（ページキーを持たない ARD 行）。両方なら n = page | N = table で {n} と {N}。空欄 = page（両方あって食い違えば警告）。どちらも ARD に入れておくこと。plan_col_header(values = list(n = ...))。
-例: n = page | N = table</t>
+          <t xml:space="preserve">Which population {n} in the column header is, for a table split by page (a lab parameter): page (those with that page's data), table (the analysis set), or both as n = page | N = table for {n} and {N}; blank: page (warns when both exist and differ). Both must be in the ARD.
+Example: n = page | N = table</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A column for people, on any sheet; never read. Any other column a sheet does not read is an error (a mistyped header).</t>
         </r>
       </text>
     </comment>
@@ -199,6 +227,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -207,8 +248,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">変数名（解析変数・列キー・ラベル列名）。
-例: AGEGR1</t>
+          <t xml:space="preserve">The variable's name.
+Example: AGEGR1</t>
         </r>
       </text>
     </comment>
@@ -220,8 +261,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">変数名の代わりに表示する文字。
-例: Age (years)</t>
+          <t xml:space="preserve">What prints for its name (plan_labels()); blank: the name.
+Example: Age (years)</t>
         </r>
       </text>
     </comment>
@@ -233,8 +274,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">変数の出現順（数値）。
-例: 1</t>
+          <t xml:space="preserve">Its place among the variables (a number); blank: the data's order.
+Example: 1</t>
         </r>
       </text>
     </comment>
@@ -246,8 +287,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">値の並び順。
-例: Grade 0 | Grade 1 | Total</t>
+          <t xml:space="preserve">Its values in print order, | between them (plan_levels()); blank: the data's order.
+Example: Grade 0 | Grade 1 | Total</t>
         </r>
       </text>
     </comment>
@@ -261,6 +302,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -269,8 +323,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">対象。変数名、または continuous / categorical、空欄 = すべてのデフォルト。
-例: continuous</t>
+          <t xml:space="preserve">What the template is for: a variable, continuous / categorical (every variable of that kind); blank: every variable.
+Example: continuous</t>
         </r>
       </text>
     </comment>
@@ -282,8 +336,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">ARD の context で絞るとき（同じ変数を 2 通りに集計した場合など）。
-例: summary</t>
+          <t xml:space="preserve">Only the ARD rows of this context (one variable summarised two ways); blank: any.
+Example: summary</t>
         </r>
       </text>
     </comment>
@@ -295,8 +349,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">行ラベル。空欄 = 水準ごとに 1 行（ラベルは水準名）。
-例: Mean (SD)</t>
+          <t xml:space="preserve">The row's label; blank: one row a level, labelled by the level.
+Example: Mean (SD)</t>
         </r>
       </text>
     </comment>
@@ -308,8 +362,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">条件（R の式）。成り立つときだけこの行を使う。空欄 = 無条件。
-例: n == 0</t>
+          <t xml:space="preserve">An R condition on the statistics; the row is used only when it holds; blank: always.
+Example: n == 0</t>
         </r>
       </text>
     </comment>
@@ -321,8 +375,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">セルの書き方。{統計量:書式} を埋め込む。
-例: {mean} ({sd})</t>
+          <t xml:space="preserve">The cell's text with {statistic:format} tokens.
+Example: {mean} ({sd})</t>
         </r>
       </text>
     </comment>
@@ -334,8 +388,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">書式のないトークンの小数桁。カンマ区切りでトークンごと。
-例: 2,3</t>
+          <t xml:space="preserve">Decimals of a token with no format, a comma between tokens; blank: plan_digits().
+Example: 2,3</t>
         </r>
       </text>
     </comment>
@@ -347,8 +401,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">有効桁（digits より優先）。
-例: 4</t>
+          <t xml:space="preserve">Significant digits (wins over digits); blank: none.
+Example: 4</t>
         </r>
       </text>
     </comment>
@@ -362,6 +416,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -370,8 +437,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。
-例: 26 / group_force / " (Cont.)"</t>
+          <t xml:space="preserve">Rows a page (plan_paginate_rows(max_rows = )), a whole number; blank: as_rtftables()' default.
+Example: 26</t>
         </r>
       </text>
     </comment>
@@ -383,8 +450,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。
-例: 26 / group_force / " (Cont.)"</t>
+          <t xml:space="preserve">How a page break may cut: group_safe / group_force / rows / ... (plan_paginate_rows(split = )); blank: as_rtftables()' default.
+Example: group_force</t>
         </r>
       </text>
     </comment>
@@ -396,8 +463,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。
-例: 26 / group_force / " (Cont.)"</t>
+          <t xml:space="preserve">Row positions to cut before, | between them, with pages_split = rows (plan_paginate_rows(break_before = )); blank: none.
+Example: 20 | 40</t>
         </r>
       </text>
     </comment>
@@ -409,8 +476,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_rows() の max_rows / split / min_group_rows / cont_label。先頭・末尾の空白を残すときは引用符で囲む。値ごとの改ページは group_page。
-例: 26 / group_force / " (Cont.)"</t>
+          <t xml:space="preserve">Rows of a group kept together at the foot of a page, a whole number (plan_paginate_rows(min_group_rows = )); blank: the default.
+Example: 2</t>
         </r>
       </text>
     </comment>
@@ -422,8 +489,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">group_page = TRUE で group_col（空欄なら一番外の行キー）の値ごとに改ページ（plan_paginate_group の col / keep）。group_keep = FALSE でその列を表示しない。
-例: TRUE / PARAM / FALSE</t>
+          <t xml:space="preserve">Appended to a group label continued on the next page (plan_paginate_rows(cont_label = )); quote it to keep leading spaces; blank: none.
+Example: " (Cont.)"</t>
         </r>
       </text>
     </comment>
@@ -435,8 +502,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_row_group() の mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。グループの列は行キーから決まる。
-例: value / 1 | 2</t>
+          <t xml:space="preserve">With group_page = TRUE: the column whose values each start a page (plan_paginate_group(col = )); blank: the outermost row key.
+Example: PARAM</t>
         </r>
       </text>
     </comment>
@@ -448,8 +515,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_row_group() の mode / collapse。collapse は TRUE か列（名前・位置）の | 区切り。グループの列は行キーから決まる。
-例: value / 1 | 2</t>
+          <t xml:space="preserve">How groups print (plan_row_group(mode = )): value / indent / ...; blank: the default.
+Example: indent</t>
         </r>
       </text>
     </comment>
@@ -461,8 +528,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">group_page = TRUE で group_col（空欄なら一番外の行キー）の値ごとに改ページ（plan_paginate_group の col / keep）。group_keep = FALSE でその列を表示しない。
-例: TRUE / PARAM / FALSE</t>
+          <t xml:space="preserve">TRUE, or the columns (names or positions, | between them) whose repeated values print once (plan_row_group(collapse = )); blank: none.
+Example: 1 | 2</t>
         </r>
       </text>
     </comment>
@@ -474,8 +541,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">group_page = TRUE で group_col（空欄なら一番外の行キー）の値ごとに改ページ（plan_paginate_group の col / keep）。group_keep = FALSE でその列を表示しない。
-例: TRUE / PARAM / FALSE</t>
+          <t xml:space="preserve">TRUE / FALSE: one page per value of group_col (plan_paginate_group()); blank: FALSE.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -487,8 +554,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_blanks() の where / first / last / counted。
-例: between_groups / TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: with group_page, FALSE leaves the group column unprinted (plan_paginate_group(keep = )); blank: TRUE.
+Example: FALSE</t>
         </r>
       </text>
     </comment>
@@ -500,8 +567,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_blanks() の where / first / last / counted。
-例: between_groups / TRUE</t>
+          <t xml:space="preserve">Where blank rows go: a named rule such as between_groups (plan_blanks(where = )); blank: none.
+Example: between_groups</t>
         </r>
       </text>
     </comment>
@@ -513,8 +580,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_blanks() の where / first / last / counted。
-例: between_groups / TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: a blank row before the first row (plan_blanks(first = )); blank: the default.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -526,8 +593,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_blanks() の where / first / last / counted。
-例: between_groups / TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: a blank row after the last row (plan_blanks(last = )); blank: the default.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -539,8 +606,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_stub() の vars / name / indent / group_summary / before。
-例: row_label / TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: blank rows count towards pages_max_rows (plan_blanks(counted = )); blank: the default.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -552,8 +619,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_stub() の vars / name / indent / group_summary / before。
-例: row_label / TRUE</t>
+          <t xml:space="preserve">The row-key columns folded into one stub column, | between them (plan_stub(vars = )); blank: the row keys.
+Example: group1 | label</t>
         </r>
       </text>
     </comment>
@@ -565,8 +632,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_stub() の vars / name / indent / group_summary / before。
-例: row_label / TRUE</t>
+          <t xml:space="preserve">The stub column's name (plan_stub(name = )); blank: the default.
+Example: row_label</t>
         </r>
       </text>
     </comment>
@@ -578,8 +645,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_stub() の vars / name / indent / group_summary / before。
-例: row_label / TRUE</t>
+          <t xml:space="preserve">Spaces a level is indented in the stub, a whole number (plan_stub(indent = )); blank: the default.
+Example: 2</t>
         </r>
       </text>
     </comment>
@@ -591,8 +658,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_stub() の vars / name / indent / group_summary / before。
-例: row_label / TRUE</t>
+          <t xml:space="preserve">How a group's summary row shows in the stub (plan_stub(group_summary = )); blank: the default.
+Example: header</t>
         </r>
       </text>
     </comment>
@@ -604,8 +671,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。
-例: 16 | 29 / 1 | 2</t>
+          <t xml:space="preserve">TRUE / FALSE: fold the stub before cell styles and sorting see the rows (plan_stub(before = )); blank: FALSE.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -617,8 +684,21 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。
-例: 16 | 29 / 1 | 2</t>
+          <t xml:space="preserve">Value columns a column page, a whole number (plan_paginate_cols(every = )); blank: no column pages.
+Example: 4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The columns to cut before (names or positions), | between them (plan_paginate_cols(at = )).
+Example: 16 | 29</t>
         </r>
       </text>
     </comment>
@@ -630,8 +710,60 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">plan_paginate_cols() の every / at / carry / order（列方向のページ分割）。
-例: 16 | 29 / 1 | 2</t>
+          <t xml:space="preserve">Columns printed on every column page (names or positions), | between them (plan_paginate_cols(keep = )); blank: the stub.
+Example: 1 | 2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The order the axes nest in, outermost first: group / rows / cols, or across / down (plan_paginate_cols(order = )); | between them; blank: the default.
+Example: across</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A separator in the column names: one column page per key before it (plan_paginate_cols(cut_by = )).
+Example: ____</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: TRUE puts every column page on page 1's width scale, FALSE keeps each column's width (plan_paginate_cols(fit = )); blank: TRUE.
+Example: FALSE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: FALSE never cuts inside a spanning header cell (plan_paginate_cols(allow_span_break = )); blank: TRUE.
+Example: FALSE</t>
         </r>
       </text>
     </comment>
@@ -645,6 +777,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -653,8 +798,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">列名、または .values。
-例: row_label</t>
+          <t xml:space="preserve">A column name, or .values.
+Example: row_label</t>
         </r>
       </text>
     </comment>
@@ -666,8 +811,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">相対幅。幅を書くなら印字される全列に必要（.values でまとめて指定できる）。
-例: 5</t>
+          <t xml:space="preserve">Relative width (a number; plan_columns(widths = )). Give one to every printed column (.values covers the value columns); blank: rtfreporter's widths.
+Example: 5</t>
         </r>
       </text>
     </comment>
@@ -679,8 +824,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">TRUE で行見出しの列。plan_columns(row_title = )。
-例: TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: a row-title column (plan_columns(row_title = )); blank: FALSE.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -692,8 +837,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">TRUE で小数点を揃える（set_decimal_split）。
-例: TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: align the decimal points (plan_columns(decimal = )); blank: FALSE.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -705,8 +850,291 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">TRUE で処理には使うが印字しない。
-例: TRUE</t>
+          <t xml:space="preserve">TRUE / FALSE: used, not printed (plan_hide()); blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The table's rules: tfl (header top and bottom, a bottom rule on the last row) or none; blank: tfl.
+Example: tfl</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: realign n (xx.x) count / percent cells to one width; blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: size each column to its widest content (plan_columns(auto_width = )); an explicit rel_width wins; blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Data row height in twips (1/1440 inch); blank: from the font size.
+Example: 240</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: TRUE exact (clipped), FALSE at least; blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Column-header row height in twips; blank: row_height_twips.
+Example: 300</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Blank separator row height in twips; blank: row_height_twips.
+Example: 120</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Left cell padding in twips; blank: 0.
+Example: 60</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Right cell padding in twips; blank: 0.
+Example: 60</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Font family of the table; blank: the document's (Courier).
+Example: Arial</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Font size in half-points (18 = 9 pt); blank: the document's.
+Example: 16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Placement of the table: left / center / right; blank: left.
+Example: center</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Vertical alignment in a cell: bottom / top / center; blank: bottom.
+Example: top</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Cell-text markup, one of script (^{} _{} as super / subscript), relational (&gt;= &lt;= as symbols), all, none; blank: the document's (script).
+Example: all</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">One of detect (an all-empty data row prints as one blank row), collapse (a run of blank rows prints as one), none; blank: both detect and collapse.
+Example: none</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The column header's rules: sides from top | bottom | left | right, or none; blank: border's.
+Example: top | bottom</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The spanning header cells' rules: sides, or none; blank: border's.
+Example: bottom</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The body rows' rules: sides, or none; blank: border's.
+Example: none</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The first body row's rules: sides, or none; blank: border's.
+Example: top</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The last body row's rules: sides, or none; blank: border's.
+Example: bottom</t>
         </r>
       </text>
     </comment>
@@ -720,6 +1148,19 @@
     <author>tflspec</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -728,8 +1169,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">ヘッダーの行番号（1 = 一番上）。
-例: 1</t>
+          <t xml:space="preserve">The columns styled, | between them (.values = every value column); blank: every column.
+Example: Placebo | .values</t>
         </r>
       </text>
     </comment>
@@ -741,8 +1182,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">セルが乗る列。列名 / .values（値の列すべて）/ 位置（3、3:31、3:last）/ KEY = 値（そのキーがその値の列）を | 区切りで。
-例: .values / grp1 | grp2 / variable = n</t>
+          <t xml:space="preserve">TRUE / FALSE: TRUE styles the column header instead of the body; blank: FALSE.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -754,8 +1195,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">空欄 = cols 全体で 1 セル。each = 列ごとに 1 セル。キー名 = そのキーの値ごとに 1 セル（群のスパナー）。
-例: TR01AG1</t>
+          <t xml:space="preserve">An R condition over the table's columns choosing the rows; blank: every row. Two rows with a where may not set the same look: join their conditions with |.
+Example: label == "Any TEAE"</t>
         </r>
       </text>
     </comment>
@@ -767,8 +1208,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">表示文字。改行は Alt+Enter か \n。{col} {col1} {col2} {n} {n:sum} が使える。{n} を使うと N は ARD から取る。先頭の空白は引用符で囲む。
-例: {col1}\n(N={n:sum})</t>
+          <t xml:space="preserve">TRUE / FALSE; blank: unchanged.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -780,8 +1221,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">col_cell() / rtf_border() と同じ（single / none など）。
-例: single</t>
+          <t xml:space="preserve">TRUE / FALSE; blank: unchanged.
+Example: TRUE</t>
         </r>
       </text>
     </comment>
@@ -793,8 +1234,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">col_cell() / rtf_border() と同じ（single / none など）。
-例: single</t>
+          <t xml:space="preserve">left / center / right; blank: unchanged.
+Example: center</t>
         </r>
       </text>
     </comment>
@@ -806,8 +1247,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">col_cell() / rtf_border() と同じ（single / none など）。
-例: single</t>
+          <t xml:space="preserve">Text colour, #RRGGBB; blank: unchanged.
+Example: #CC0000</t>
         </r>
       </text>
     </comment>
@@ -819,8 +1260,135 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">col_cell() / rtf_border() と同じ（single / none など）。
-例: single</t>
+          <t xml:space="preserve">Cell shading, #RRGGBB; blank: unchanged.
+Example: #EEEEEE</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The header row, a whole number (1 = the top).
+Example: 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The columns the cell sits on: a name, .values (every value column), a position or range (3, 3:31, 3:last), or KEY = value (the columns whose key has that value); | between them.
+Example: .values</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Blank: one cell over cols; each: one cell a column; a key's name: one cell per value of that key (a spanner).
+Example: TR01AG1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">What prints; a line break is Alt+Enter or \n. Tokens: {col} {col1} {col2} (the column's keys), {n} {n1} {n2} (the population at that depth, read from the ARD), {n:sum} (the total over the cell's columns). Quote it to keep leading spaces.
+Example: {col1}\n(N={n:sum})</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">left / center / right (col_cell()); blank: the default.
+Example: center</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE; blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The cell's top rule: single / double / none ... (rtf_border()); blank: the header's.
+Example: single</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The cell's bottom rule, as border_top.
+Example: single</t>
         </r>
       </text>
     </comment>
@@ -829,7 +1397,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -936,6 +1504,9 @@
     <t xml:space="preserve">pages_split</t>
   </si>
   <si>
+    <t xml:space="preserve">pages_break_before</t>
+  </si>
+  <si>
     <t xml:space="preserve">pages_min_group_rows</t>
   </si>
   <si>
@@ -996,6 +1567,15 @@
     <t xml:space="preserve">colpages_order</t>
   </si>
   <si>
+    <t xml:space="preserve">colpages_cut_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colpages_fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colpages_allow_span_break</t>
+  </si>
+  <si>
     <t xml:space="preserve">TRUE</t>
   </si>
   <si>
@@ -1008,7 +1588,7 @@
     <t xml:space="preserve">column</t>
   </si>
   <si>
-    <t xml:space="preserve">width</t>
+    <t xml:space="preserve">rel_width</t>
   </si>
   <si>
     <t xml:space="preserve">row_title</t>
@@ -1089,6 +1669,27 @@
     <t xml:space="preserve">border_last_row</t>
   </si>
   <si>
+    <t xml:space="preserve">header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">where</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">italic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">align</t>
+  </si>
+  <si>
+    <t xml:space="preserve">color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">background</t>
+  </si>
+  <si>
     <t xml:space="preserve">line</t>
   </si>
   <si>
@@ -1096,12 +1697,6 @@
   </si>
   <si>
     <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">align</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bold</t>
   </si>
   <si>
     <t xml:space="preserve">border_top</t>
@@ -1483,6 +2078,33 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -1739,6 +2361,18 @@
       <c r="W1" t="s">
         <v>54</v>
       </c>
+      <c r="X1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -1751,31 +2385,35 @@
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
-      <c r="I2" t="s">
-        <v>55</v>
-      </c>
+      <c r="I2"/>
       <c r="J2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2"/>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2"/>
       <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2"/>
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
       <c r="O2"/>
-      <c r="P2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q2"/>
+      <c r="P2"/>
+      <c r="Q2" t="s">
+        <v>61</v>
+      </c>
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2"/>
       <c r="U2"/>
       <c r="V2"/>
       <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1794,19 +2432,19 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2">
@@ -1814,10 +2452,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -1828,10 +2466,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1854,64 +2492,64 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="R1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="S1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="T1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="U1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
@@ -1920,7 +2558,7 @@
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -1944,6 +2582,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1957,107 +2596,29 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4" t="s">
         <v>96</v>
       </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2073,22 +2634,114 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>